--- a/08_project/pdp_link.xlsx
+++ b/08_project/pdp_link.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10630"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://centralgroup-my.sharepoint.com/personal/thao_thimai_dang_vn_centralretail_com/Documents/WORKING FOLDER/1. HAND OVER/3. REPORT DAILY/01_code/loutruong/08_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{E4E59CD0-BEC9-4F6D-B00F-1F7F9E52AD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3DAA1DC-F578-41D5-AFE7-DA96196DF726}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{E4E59CD0-BEC9-4F6D-B00F-1F7F9E52AD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49EFBCAB-7961-554C-ABAC-D718E8270BE0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE45E9E3-E17F-431B-8DDF-A7805D077ADE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{FE45E9E3-E17F-431B-8DDF-A7805D077ADE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -465,13 +465,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E58997-DA0A-4296-9C60-55B2AD3133F6}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="20.7109375" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,7 +484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -493,7 +495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -504,7 +506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -515,7 +517,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -526,7 +528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -537,7 +539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
